--- a/audit-projects/ar-confirmation-simulation/AR_Confirmation_Workpaper_2026.xlsx
+++ b/audit-projects/ar-confirmation-simulation/AR_Confirmation_Workpaper_2026.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Summary" sheetId="1" r:id="R532724aa1e4f489c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AR Population" sheetId="2" r:id="R762c68720ddb43f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample Selection" sheetId="3" r:id="Rdd8334a04e1042b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confirmation Log" sheetId="4" r:id="R898f3b78ea7b4873"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alternative Procedures" sheetId="5" r:id="R6cfc3009cc6f4089"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exceptions" sheetId="6" r:id="Re43f4f8b10b04ced"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Checks" sheetId="7" r:id="Re9c631b5ee8445fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Summary" sheetId="1" r:id="R727c02bbe6d344d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AR Population" sheetId="2" r:id="R10e2cd72566a425b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample Selection" sheetId="3" r:id="Rbe26615d70e747f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confirmation Log" sheetId="4" r:id="Re05ca52bedc74b2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alternative Procedures" sheetId="5" r:id="R2b85c321bfd041b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exceptions" sheetId="6" r:id="R268e46b3f6e8474f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Checks" sheetId="7" r:id="Rae26e6d81b2f425f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2004,7 +2004,7 @@
         <x:color rgb="FF2E7D32"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF5EA"/>
         </x:patternFill>
       </x:fill>
@@ -2015,7 +2015,7 @@
         <x:color rgb="FFB42318"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCECEC"/>
         </x:patternFill>
       </x:fill>
@@ -2026,7 +2026,7 @@
         <x:color rgb="FF6B5CA5"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF1EEFA"/>
         </x:patternFill>
       </x:fill>
@@ -2037,7 +2037,7 @@
         <x:color rgb="FFB42318"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCECEC"/>
         </x:patternFill>
       </x:fill>
@@ -2048,7 +2048,7 @@
         <x:color rgb="FF2E7D32"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF5EA"/>
         </x:patternFill>
       </x:fill>
@@ -2059,7 +2059,7 @@
         <x:color rgb="FF2A7F78"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE8F5F2"/>
         </x:patternFill>
       </x:fill>
@@ -2070,7 +2070,7 @@
         <x:color rgb="FFB42318"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCECEC"/>
         </x:patternFill>
       </x:fill>
@@ -2081,7 +2081,7 @@
         <x:color rgb="FFB76E00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4E5"/>
         </x:patternFill>
       </x:fill>
@@ -2092,7 +2092,7 @@
         <x:color rgb="FF2E7D32"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF5EA"/>
         </x:patternFill>
       </x:fill>
@@ -2103,7 +2103,7 @@
         <x:color rgb="FFB42318"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCECEC"/>
         </x:patternFill>
       </x:fill>
@@ -2114,7 +2114,7 @@
         <x:color rgb="FFFFFFFF"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FF2E7D32"/>
         </x:patternFill>
       </x:fill>
@@ -2125,7 +2125,7 @@
         <x:color rgb="FF2E7D32"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF5EA"/>
         </x:patternFill>
       </x:fill>
@@ -2136,7 +2136,7 @@
         <x:color rgb="FFB42318"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCECEC"/>
         </x:patternFill>
       </x:fill>
@@ -2316,7 +2316,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9ab530b42fc3455a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R319135681f0e4d60"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2802,7 +2802,7 @@
         <x:v>Prepared by</x:v>
       </x:c>
       <x:c r="G4" s="12" t="str">
-        <x:v>SanDAce07</x:v>
+        <x:v>Sandesh Lama Tamang</x:v>
       </x:c>
       <x:c r="H4" s="12"/>
       <x:c r="I4" s="12"/>
@@ -3369,8 +3369,8 @@
     <x:mergeCell ref="A46:O48"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fc2d6d4deb94e20"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7759131673e641d6"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cee72e010fe4b78"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ebb1a46461b4c5d"/>
 </x:worksheet>
 </file>
 
@@ -4090,7 +4090,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52d79eed69d74cd9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2b422e91cc34d7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4448,9 +4448,9 @@
     <x:cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="High"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bb5b4c01e784dd1"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cf7391438dd4421"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra257bd75060f4ce1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f329c51bba84d9e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4888,7 +4888,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47c09cf5692f41b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6dd4de217b84f6f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5194,7 +5194,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re984286278414275"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf7ff88639ad4435"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5512,7 +5512,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a8355f3a8e84947"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b4f1ebfbb3241b9"/>
 </x:worksheet>
 </file>
 
